--- a/artfynd/A 19109-2023 artfynd.xlsx
+++ b/artfynd/A 19109-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19109-2023 artfynd.xlsx
+++ b/artfynd/A 19109-2023 artfynd.xlsx
@@ -4630,7 +4630,7 @@
         <v>109572122</v>
       </c>
       <c r="B34" t="n">
-        <v>57575</v>
+        <v>58166</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4643,21 +4643,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401910.632384781</v>
+        <v>401911</v>
       </c>
       <c r="R34" t="n">
-        <v>6872796.056896448</v>
+        <v>6872796</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>

--- a/artfynd/A 19109-2023 artfynd.xlsx
+++ b/artfynd/A 19109-2023 artfynd.xlsx
@@ -4630,7 +4630,7 @@
         <v>109572122</v>
       </c>
       <c r="B34" t="n">
-        <v>58166</v>
+        <v>58176</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 19109-2023 artfynd.xlsx
+++ b/artfynd/A 19109-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4228,10 +4228,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109547319</v>
+        <v>109571900</v>
       </c>
       <c r="B31" t="n">
-        <v>95511</v>
+        <v>56395</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4240,31 +4240,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221944</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4272,10 +4276,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401146.6949454338</v>
+        <v>401757.4090313207</v>
       </c>
       <c r="R31" t="n">
-        <v>6873048.692096949</v>
+        <v>6872808.947807441</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4307,7 +4311,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4317,7 +4321,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4326,7 +4330,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4337,7 +4340,22 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Granskog. Fjällnära skog</t>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4355,10 +4373,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109571900</v>
+        <v>109572201</v>
       </c>
       <c r="B32" t="n">
-        <v>56395</v>
+        <v>95519</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4367,35 +4385,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4403,10 +4417,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>401757.4090313207</v>
+        <v>402054.7921150271</v>
       </c>
       <c r="R32" t="n">
-        <v>6872808.947807441</v>
+        <v>6872861.05767492</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4438,7 +4452,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4448,7 +4462,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4457,6 +4471,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4467,22 +4482,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Fjällnära skog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109572201</v>
+        <v>109572122</v>
       </c>
       <c r="B33" t="n">
-        <v>95519</v>
+        <v>58176</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4516,27 +4516,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>208249</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4544,10 +4557,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>402054.7921150271</v>
+        <v>401911</v>
       </c>
       <c r="R33" t="n">
-        <v>6872861.05767492</v>
+        <v>6872796</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4579,7 +4592,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4589,7 +4602,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4609,7 +4622,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Fjällnära skog</t>
+          <t>Granskog med rörligt ytvatten. Fjällnära skog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4627,10 +4640,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109572122</v>
+        <v>109571555</v>
       </c>
       <c r="B34" t="n">
-        <v>58176</v>
+        <v>56395</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4639,42 +4652,33 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>208249</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4684,10 +4688,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401911</v>
+        <v>401531.5218797573</v>
       </c>
       <c r="R34" t="n">
-        <v>6872796</v>
+        <v>6872883.225150374</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4719,7 +4723,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4729,7 +4733,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4738,7 +4742,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4749,7 +4752,22 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Granskog med rörligt ytvatten. Fjällnära skog.</t>
+          <t>Grannaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4767,14 +4785,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109571555</v>
+        <v>109534899</v>
       </c>
       <c r="B35" t="n">
-        <v>56395</v>
+        <v>78098</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4783,45 +4801,44 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storfjäten, Storfjäten, Idre, Hjd</t>
+          <t>Storfjäten, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>401531.5218797573</v>
+        <v>401361.9018477423</v>
       </c>
       <c r="R35" t="n">
-        <v>6872883.225150374</v>
+        <v>6872639.266626423</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4850,7 +4867,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4860,7 +4877,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4871,31 +4888,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Grannaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4912,10 +4904,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109534899</v>
+        <v>109535369</v>
       </c>
       <c r="B36" t="n">
-        <v>78098</v>
+        <v>78072</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4928,21 +4920,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4959,13 +4951,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>401361.9018477423</v>
+        <v>401215.9496293855</v>
       </c>
       <c r="R36" t="n">
-        <v>6872639.266626423</v>
+        <v>6872870.266130998</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4994,7 +4986,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5004,7 +4996,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5031,10 +5023,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>109535369</v>
+        <v>109571809</v>
       </c>
       <c r="B37" t="n">
-        <v>78072</v>
+        <v>78098</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5047,21 +5039,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5074,14 +5066,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storfjäten, Hjd</t>
+          <t>Storfjäten, Storfjäten, Idre, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>401215.9496293855</v>
+        <v>401609.1650895413</v>
       </c>
       <c r="R37" t="n">
-        <v>6872870.266130998</v>
+        <v>6872912.497432139</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5113,7 +5105,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5123,7 +5115,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5132,8 +5124,39 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Tallnaturskog.</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe.</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På kolad tallstubbe.</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5150,14 +5173,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>109571809</v>
+        <v>109596193</v>
       </c>
       <c r="B38" t="n">
-        <v>78098</v>
+        <v>56395</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5166,44 +5189,49 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storfjäten, Storfjäten, Idre, Hjd</t>
+          <t>Storfjätan, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>401609.1650895413</v>
+        <v>400207.4023804629</v>
       </c>
       <c r="R38" t="n">
-        <v>6872912.497432139</v>
+        <v>6873101.529959369</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5227,22 +5255,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5251,39 +5279,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Tallnaturskog.</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe.</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På kolad tallstubbe.</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5300,10 +5297,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>109596193</v>
+        <v>109596438</v>
       </c>
       <c r="B39" t="n">
-        <v>56395</v>
+        <v>95519</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5312,39 +5309,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5358,7 +5347,7 @@
         <v>6873101.529959369</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5387,7 +5376,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5397,7 +5386,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5424,54 +5413,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>109596438</v>
+        <v>109533708</v>
       </c>
       <c r="B40" t="n">
-        <v>95519</v>
+        <v>78098</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storfjätan, Hjd</t>
+          <t>Storfjäten , Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>400207.4023804629</v>
+        <v>401521.0033803247</v>
       </c>
       <c r="R40" t="n">
-        <v>6873101.529959369</v>
+        <v>6872764.035010103</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5498,22 +5490,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Växer på torraka i tallnaturskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5540,14 +5537,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>109533708</v>
+        <v>109591485</v>
       </c>
       <c r="B41" t="n">
-        <v>78098</v>
+        <v>56395</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5556,44 +5553,49 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storfjäten , Hjd</t>
+          <t>Storfjäten, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>401521.0033803247</v>
+        <v>400565.0161518555</v>
       </c>
       <c r="R41" t="n">
-        <v>6872764.035010103</v>
+        <v>6872812.551955354</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5617,27 +5619,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer på torraka i tallnaturskog</t>
+          <t>Hackmärken på grov gran i fuktig sänka.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5664,32 +5666,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>109591485</v>
+        <v>109590311</v>
       </c>
       <c r="B42" t="n">
-        <v>56395</v>
+        <v>57150</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>208260</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5702,11 +5704,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5716,13 +5719,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>400565.0161518555</v>
+        <v>400859.7407940112</v>
       </c>
       <c r="R42" t="n">
-        <v>6872812.551955354</v>
+        <v>6872982.717832778</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5751,7 +5754,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5761,12 +5764,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hackmärken på grov gran i fuktig sänka.</t>
+          <t>Ormen ligger skyddad i lä. Stördes inte av min närvaro. Tallnaturskog.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5793,10 +5796,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>109590311</v>
+        <v>109588318</v>
       </c>
       <c r="B43" t="n">
-        <v>57150</v>
+        <v>77605</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5805,40 +5808,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>208260</v>
+        <v>967</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5846,10 +5839,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>400859.7407940112</v>
+        <v>400881.0078615721</v>
       </c>
       <c r="R43" t="n">
-        <v>6872982.717832778</v>
+        <v>6873114.287772141</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5881,7 +5874,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5891,12 +5884,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ormen ligger skyddad i lä. Stördes inte av min närvaro. Tallnaturskog.</t>
+          <t>Växer på torraka tillsammans med vedflamlav. Tallnaturskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5923,10 +5916,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>109588318</v>
+        <v>109591251</v>
       </c>
       <c r="B44" t="n">
-        <v>77605</v>
+        <v>78098</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5939,26 +5932,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5966,13 +5963,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>400881.0078615721</v>
+        <v>400887.83550034</v>
       </c>
       <c r="R44" t="n">
-        <v>6873114.287772141</v>
+        <v>6872750.436704724</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6001,7 +5998,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6011,12 +6008,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Växer på torraka tillsammans med vedflamlav. Tallnaturskog.</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6043,7 +6035,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>109591251</v>
+        <v>109595405</v>
       </c>
       <c r="B45" t="n">
         <v>78098</v>
@@ -6086,14 +6078,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storfjäten, Hjd</t>
+          <t>Broktjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>400887.83550034</v>
+        <v>400306.0816236691</v>
       </c>
       <c r="R45" t="n">
-        <v>6872750.436704724</v>
+        <v>6873140.973492022</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -6125,7 +6117,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6135,7 +6127,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6162,14 +6154,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>109595405</v>
+        <v>109633368</v>
       </c>
       <c r="B46" t="n">
-        <v>78098</v>
+        <v>56395</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6178,44 +6170,45 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Broktjärnen, Hjd</t>
+          <t>Storfjäten, Storfjäten, Idre, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>400306.0816236691</v>
+        <v>400194.9944916581</v>
       </c>
       <c r="R46" t="n">
-        <v>6873140.973492022</v>
+        <v>6872999.810241123</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6244,7 +6237,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6254,7 +6247,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hackmärken på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6265,6 +6263,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Barrblandskog. Naturskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6281,7 +6289,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>109633368</v>
+        <v>109633326</v>
       </c>
       <c r="B47" t="n">
         <v>56395</v>
@@ -6329,10 +6337,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>400194.9944916581</v>
+        <v>400180.0568112093</v>
       </c>
       <c r="R47" t="n">
-        <v>6872999.810241123</v>
+        <v>6872988.487667387</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6364,7 +6372,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6374,7 +6382,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6398,7 +6406,22 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Barrblandskog. Naturskog</t>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6413,156 +6436,6 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>109633326</v>
-      </c>
-      <c r="B48" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Storfjäten, Storfjäten, Idre, Hjd</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>400180.0568112093</v>
-      </c>
-      <c r="R48" t="n">
-        <v>6872988.487667387</v>
-      </c>
-      <c r="S48" t="n">
-        <v>5</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Idre</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hackmärken på gran</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19109-2023 artfynd.xlsx
+++ b/artfynd/A 19109-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4228,10 +4228,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109571900</v>
+        <v>109547319</v>
       </c>
       <c r="B31" t="n">
-        <v>56395</v>
+        <v>95511</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4240,35 +4240,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>221944</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4276,10 +4272,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>401757.4090313207</v>
+        <v>401146.6949454338</v>
       </c>
       <c r="R31" t="n">
-        <v>6872808.947807441</v>
+        <v>6873048.692096949</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4311,7 +4307,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4321,7 +4317,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4330,6 +4326,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4340,22 +4337,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog. Fjällnära skog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4373,10 +4355,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109572201</v>
+        <v>109571900</v>
       </c>
       <c r="B32" t="n">
-        <v>95519</v>
+        <v>56395</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4385,31 +4367,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4417,10 +4403,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>402054.7921150271</v>
+        <v>401757.4090313207</v>
       </c>
       <c r="R32" t="n">
-        <v>6872861.05767492</v>
+        <v>6872808.947807441</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4452,7 +4438,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4462,7 +4448,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4471,7 +4457,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4482,7 +4467,22 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Fjällnära skog</t>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109572122</v>
+        <v>109572201</v>
       </c>
       <c r="B33" t="n">
-        <v>58176</v>
+        <v>95519</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4516,40 +4516,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>208249</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4557,10 +4544,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>401911</v>
+        <v>402054.7921150271</v>
       </c>
       <c r="R33" t="n">
-        <v>6872796</v>
+        <v>6872861.05767492</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4592,7 +4579,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4602,7 +4589,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4622,7 +4609,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Granskog med rörligt ytvatten. Fjällnära skog.</t>
+          <t>Fjällnära skog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4640,10 +4627,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109571555</v>
+        <v>109572122</v>
       </c>
       <c r="B34" t="n">
-        <v>56395</v>
+        <v>58176</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4652,33 +4639,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>208249</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4688,10 +4684,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>401531.5218797573</v>
+        <v>401911</v>
       </c>
       <c r="R34" t="n">
-        <v>6872883.225150374</v>
+        <v>6872796</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4723,7 +4719,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4733,7 +4729,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4742,6 +4738,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4752,22 +4749,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Grannaturskog. Fjällnära</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Granskog med rörligt ytvatten. Fjällnära skog.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4785,14 +4767,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109534899</v>
+        <v>109571555</v>
       </c>
       <c r="B35" t="n">
-        <v>78098</v>
+        <v>56395</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4801,44 +4783,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storfjäten, Hjd</t>
+          <t>Storfjäten, Storfjäten, Idre, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>401361.9018477423</v>
+        <v>401531.5218797573</v>
       </c>
       <c r="R35" t="n">
-        <v>6872639.266626423</v>
+        <v>6872883.225150374</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4867,7 +4850,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4877,7 +4860,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4888,6 +4871,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Grannaturskog. Fjällnära</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4904,10 +4912,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109535369</v>
+        <v>109534899</v>
       </c>
       <c r="B36" t="n">
-        <v>78072</v>
+        <v>78098</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4920,21 +4928,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4951,13 +4959,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>401215.9496293855</v>
+        <v>401361.9018477423</v>
       </c>
       <c r="R36" t="n">
-        <v>6872870.266130998</v>
+        <v>6872639.266626423</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4986,7 +4994,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4996,7 +5004,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5023,10 +5031,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>109571809</v>
+        <v>109535369</v>
       </c>
       <c r="B37" t="n">
-        <v>78098</v>
+        <v>78072</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5039,21 +5047,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5066,14 +5074,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storfjäten, Storfjäten, Idre, Hjd</t>
+          <t>Storfjäten, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>401609.1650895413</v>
+        <v>401215.9496293855</v>
       </c>
       <c r="R37" t="n">
-        <v>6872912.497432139</v>
+        <v>6872870.266130998</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5105,7 +5113,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5115,7 +5123,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5124,39 +5132,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Tallnaturskog.</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>På kolad tallstubbe.</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På kolad tallstubbe.</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5173,14 +5150,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>109596193</v>
+        <v>109571809</v>
       </c>
       <c r="B38" t="n">
-        <v>56395</v>
+        <v>78098</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5189,49 +5166,44 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storfjätan, Hjd</t>
+          <t>Storfjäten, Storfjäten, Idre, Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>400207.4023804629</v>
+        <v>401609.1650895413</v>
       </c>
       <c r="R38" t="n">
-        <v>6873101.529959369</v>
+        <v>6872912.497432139</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5255,22 +5227,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5279,8 +5251,39 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Tallnaturskog.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>På kolad tallstubbe.</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På kolad tallstubbe.</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5297,10 +5300,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>109596438</v>
+        <v>109596193</v>
       </c>
       <c r="B39" t="n">
-        <v>95519</v>
+        <v>56395</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5309,31 +5312,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5347,7 +5358,7 @@
         <v>6873101.529959369</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5376,7 +5387,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5386,7 +5397,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5413,57 +5424,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>109533708</v>
+        <v>109596438</v>
       </c>
       <c r="B40" t="n">
-        <v>78098</v>
+        <v>95519</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storfjäten , Hjd</t>
+          <t>Storfjätan, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>401521.0033803247</v>
+        <v>400207.4023804629</v>
       </c>
       <c r="R40" t="n">
-        <v>6872764.035010103</v>
+        <v>6873101.529959369</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5490,27 +5498,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Växer på torraka i tallnaturskog</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5537,14 +5540,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>109591485</v>
+        <v>109533708</v>
       </c>
       <c r="B41" t="n">
-        <v>56395</v>
+        <v>78098</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5553,49 +5556,44 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storfjäten, Hjd</t>
+          <t>Storfjäten , Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>400565.0161518555</v>
+        <v>401521.0033803247</v>
       </c>
       <c r="R41" t="n">
-        <v>6872812.551955354</v>
+        <v>6872764.035010103</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5619,27 +5617,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Hackmärken på grov gran i fuktig sänka.</t>
+          <t>Växer på torraka i tallnaturskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5666,32 +5664,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>109590311</v>
+        <v>109591485</v>
       </c>
       <c r="B42" t="n">
-        <v>57150</v>
+        <v>56395</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>208260</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5704,12 +5702,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5719,13 +5716,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>400859.7407940112</v>
+        <v>400565.0161518555</v>
       </c>
       <c r="R42" t="n">
-        <v>6872982.717832778</v>
+        <v>6872812.551955354</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5754,7 +5751,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5764,12 +5761,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ormen ligger skyddad i lä. Stördes inte av min närvaro. Tallnaturskog.</t>
+          <t>Hackmärken på grov gran i fuktig sänka.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5796,10 +5793,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>109588318</v>
+        <v>109590311</v>
       </c>
       <c r="B43" t="n">
-        <v>77605</v>
+        <v>57150</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5808,30 +5805,40 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>967</v>
+        <v>208260</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5839,10 +5846,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>400881.0078615721</v>
+        <v>400859.7407940112</v>
       </c>
       <c r="R43" t="n">
-        <v>6873114.287772141</v>
+        <v>6872982.717832778</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5874,7 +5881,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5884,12 +5891,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Växer på torraka tillsammans med vedflamlav. Tallnaturskog.</t>
+          <t>Ormen ligger skyddad i lä. Stördes inte av min närvaro. Tallnaturskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5916,10 +5923,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>109591251</v>
+        <v>109588318</v>
       </c>
       <c r="B44" t="n">
-        <v>78098</v>
+        <v>77605</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5932,30 +5939,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5963,13 +5966,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>400887.83550034</v>
+        <v>400881.0078615721</v>
       </c>
       <c r="R44" t="n">
-        <v>6872750.436704724</v>
+        <v>6873114.287772141</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5998,7 +6001,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6008,7 +6011,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Växer på torraka tillsammans med vedflamlav. Tallnaturskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6035,7 +6043,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>109595405</v>
+        <v>109591251</v>
       </c>
       <c r="B45" t="n">
         <v>78098</v>
@@ -6078,14 +6086,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Broktjärnen, Hjd</t>
+          <t>Storfjäten, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>400306.0816236691</v>
+        <v>400887.83550034</v>
       </c>
       <c r="R45" t="n">
-        <v>6873140.973492022</v>
+        <v>6872750.436704724</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -6117,7 +6125,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6127,7 +6135,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6154,14 +6162,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>109633368</v>
+        <v>109595405</v>
       </c>
       <c r="B46" t="n">
-        <v>56395</v>
+        <v>78098</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6170,45 +6178,44 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storfjäten, Storfjäten, Idre, Hjd</t>
+          <t>Broktjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>400194.9944916581</v>
+        <v>400306.0816236691</v>
       </c>
       <c r="R46" t="n">
-        <v>6872999.810241123</v>
+        <v>6873140.973492022</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6237,7 +6244,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6247,12 +6254,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hackmärken på gran</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6263,16 +6265,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Barrblandskog. Naturskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6289,7 +6281,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>109633326</v>
+        <v>109633368</v>
       </c>
       <c r="B47" t="n">
         <v>56395</v>
@@ -6337,10 +6329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>400180.0568112093</v>
+        <v>400194.9944916581</v>
       </c>
       <c r="R47" t="n">
-        <v>6872988.487667387</v>
+        <v>6872999.810241123</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6372,7 +6364,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6382,7 +6374,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6406,22 +6398,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrblandskog. Naturskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6436,6 +6413,156 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>109633326</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56395</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Storfjäten, Storfjäten, Idre, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>400180.0568112093</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6872988.487667387</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hackmärken på gran</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19109-2023 artfynd.xlsx
+++ b/artfynd/A 19109-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109508897</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109509186</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109509439</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109510342</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109510490</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109510668</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109511147</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,6 +1602,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109511791</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1672,6 +1717,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109512323</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109512504</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1892,6 +1947,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109512679</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2028,6 +2088,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109518862</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2154,6 +2219,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109522771</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2295,6 +2365,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109522792</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2436,6 +2511,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109523155</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2551,6 +2631,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109588318</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2677,6 +2762,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109548166</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2787,6 +2877,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507453</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2897,6 +2992,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109510992</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3023,6 +3123,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633428</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3133,6 +3238,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109510558</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3243,6 +3353,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109528561</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3357,6 +3472,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109506659</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3476,6 +3596,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109533708</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3590,6 +3715,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534496</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3704,6 +3834,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534899</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3849,6 +3984,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109571809</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3963,6 +4103,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109591251</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4077,6 +4222,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109595405</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4196,6 +4346,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109512002</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4315,6 +4470,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109513992</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4434,6 +4594,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109514105</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4558,6 +4723,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109527922</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4677,6 +4847,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109535910</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4817,6 +4992,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109571555</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4962,6 +5142,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109571682</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5102,6 +5287,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109571900</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5226,6 +5416,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109591485</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5345,6 +5540,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109596193</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5479,6 +5679,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109611264</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5614,6 +5819,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633326</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5744,6 +5954,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109633368</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5863,6 +6078,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109507620</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5993,6 +6213,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109522948</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6117,6 +6342,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109590477</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6240,6 +6470,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109506382</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6374,6 +6609,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109571281</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6509,6 +6749,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109572122</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6634,6 +6879,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109590311</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6756,6 +7006,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109547943</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6874,6 +7129,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109547319</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6985,6 +7245,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109514256</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7107,6 +7372,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109572201</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7218,6 +7488,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109596438</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7328,6 +7603,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534737</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7442,8 +7722,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109535369</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>